--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
@@ -407,13 +407,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>5.53159937941633</v>
+        <v>5.69910844108087</v>
       </c>
       <c r="C6" t="n">
-        <v>0.437100804580176</v>
+        <v>0.459402166212718</v>
       </c>
       <c r="D6" t="n">
-        <v>35.7197828213133</v>
+        <v>39.0909809936463</v>
       </c>
       <c r="E6" t="n">
         <v>0.001</v>
@@ -424,10 +424,10 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>7.12360354277753</v>
+        <v>6.70638038815988</v>
       </c>
       <c r="C7" t="n">
-        <v>0.562899195419824</v>
+        <v>0.540597833787282</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -437,7 +437,7 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>12.6552029221939</v>
+        <v>12.4054888292407</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -472,13 +472,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>5.08665603177802</v>
+        <v>5.54066831925341</v>
       </c>
       <c r="C12" t="n">
-        <v>0.382137901282793</v>
+        <v>0.417706523188858</v>
       </c>
       <c r="D12" t="n">
-        <v>28.450269883044</v>
+        <v>32.9979655137359</v>
       </c>
       <c r="E12" t="n">
         <v>0.001</v>
@@ -489,10 +489,10 @@
         <v>46</v>
       </c>
       <c r="B13" t="n">
-        <v>8.22439219113496</v>
+        <v>7.72383202169124</v>
       </c>
       <c r="C13" t="n">
-        <v>0.617862098717207</v>
+        <v>0.582293476811142</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -502,7 +502,7 @@
         <v>47</v>
       </c>
       <c r="B14" t="n">
-        <v>13.311048222913</v>
+        <v>13.2645003409446</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -537,16 +537,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.342371297296679</v>
+        <v>0.357129012442449</v>
       </c>
       <c r="C18" t="n">
-        <v>0.028070446747354</v>
+        <v>0.0294459729012055</v>
       </c>
       <c r="D18" t="n">
-        <v>1.32853306709014</v>
+        <v>1.39560984307531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.231</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="19">
@@ -554,10 +554,10 @@
         <v>46</v>
       </c>
       <c r="B19" t="n">
-        <v>11.8544882816821</v>
+        <v>11.771151266856</v>
       </c>
       <c r="C19" t="n">
-        <v>0.971929553252646</v>
+        <v>0.970554027098795</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -567,7 +567,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="n">
-        <v>12.1968595789788</v>
+        <v>12.1282802792985</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>1.39560984307531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.193</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>1.39560984307531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.212</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>1.39560984307531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.199</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_21_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>1.39560984307531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.21</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="19">
